--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131740064</v>
+        <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ugglekärr Nord, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579645</v>
+        <v>579741</v>
       </c>
       <c r="R2" t="n">
-        <v>6399146</v>
+        <v>6398918</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,20 +775,122 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073558</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131740064</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ugglekärr Nord, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>579645</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6399146</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lynx Beverskog</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131740064</t>
         </is>
@@ -787,6 +899,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27568-2024 artfynd.xlsx
+++ b/artfynd/A 27568-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073558</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
